--- a/Mazandasht_v04/07_Demo.xlsx
+++ b/Mazandasht_v04/07_Demo.xlsx
@@ -2498,7 +2498,7 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="40" t="inlineStr">
         <is>
-          <t>این جدول عمداً ساده است: دو ستون بدهکار/بستانکار با قاعده‌های ثابت پر می‌شوند. در فایل اصلی همین کار را جدول عملیات INFO انجام می‌دهد.</t>
+          <t>این جدول عمداً ساده است: دو ستون بدهکار/بستانکار با قاعده‌های ثابت پر می‌شوند. در فایل اصلی همین کار را جدول عملیات فایل مادر 00_Master انجام می‌دهد.</t>
         </is>
       </c>
       <c r="B20" s="81" t="n"/>
@@ -2900,7 +2900,7 @@
     <row r="3">
       <c r="A3" s="92" t="inlineStr">
         <is>
-          <t>MAZANDASHT · INFO MASTER DATA (READ ONLY)</t>
+          <t>MAZANDASHT · فایل مادر 00_Master MASTER DATA (READ ONLY)</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>برای کار واقعی: 01_Entry.xlsx را باز کنید؛ همان قواعد با جدول عملیات INFO اجرا می‌شود.</t>
+          <t>برای کار واقعی: 01_Entry.xlsx را باز کنید؛ همان قواعد با جدول عملیات فایل مادر 00_Master اجرا می‌شود.</t>
         </is>
       </c>
       <c r="B27" s="81" t="n"/>

--- a/Mazandasht_v04/07_Demo.xlsx
+++ b/Mazandasht_v04/07_Demo.xlsx
@@ -55,7 +55,7 @@
     <definedName name="ParamTbl">Sync!$AO$10:$AP$21</definedName>
     <definedName name="ProductTbl">Sync!$AH$10:$AI$29</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Home'!$7:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Home'!$A$1:$J$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Home'!$A$1:$J$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Reg'!$A$9:$M$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Reg'!$7:$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Reg'!$A$1:$M$22</definedName>
@@ -485,7 +485,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -804,11 +804,55 @@
         <color rgb="00D8D2C2"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D8D2C2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D8D2C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D8D2C2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D8D2C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D8D2C2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D8D2C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D8D2C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D8D2C2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -1089,8 +1133,10 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="20" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1507,10 +1553,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.7109375" customWidth="1" min="1" max="10"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -1717,60 +1772,86 @@
           <t>فایل مادر  00_Master</t>
         </is>
       </c>
-      <c r="C24" s="103" t="inlineStr">
+      <c r="B24" s="104" t="n"/>
+      <c r="C24" s="105" t="n"/>
+      <c r="D24" s="103" t="inlineStr">
         <is>
           <t>دفتر ثبت  01_Entry</t>
         </is>
       </c>
-      <c r="E24" s="103" t="inlineStr">
+      <c r="E24" s="104" t="n"/>
+      <c r="F24" s="105" t="n"/>
+      <c r="G24" s="103" t="inlineStr">
         <is>
           <t>بانک  02_Bank</t>
         </is>
       </c>
-      <c r="G24" s="103" t="inlineStr">
-        <is>
-          <t>گزارش‌ها  03_Report</t>
-        </is>
-      </c>
-      <c r="I24" s="103" t="inlineStr">
-        <is>
-          <t>فاکتورها  04_Inv</t>
-        </is>
-      </c>
+      <c r="H24" s="104" t="n"/>
+      <c r="I24" s="105" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="103" t="inlineStr">
         <is>
+          <t>گزارش‌ها  03_Report</t>
+        </is>
+      </c>
+      <c r="B25" s="104" t="n"/>
+      <c r="C25" s="105" t="n"/>
+      <c r="D25" s="103" t="inlineStr">
+        <is>
+          <t>فاکتورها  04_Inv</t>
+        </is>
+      </c>
+      <c r="E25" s="104" t="n"/>
+      <c r="F25" s="105" t="n"/>
+      <c r="G25" s="103" t="inlineStr">
+        <is>
           <t>تراز  05_Bal</t>
         </is>
       </c>
-      <c r="C25" s="103" t="inlineStr">
+      <c r="H25" s="104" t="n"/>
+      <c r="I25" s="105" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="103" t="inlineStr">
         <is>
           <t>خریداران  06_Buyers</t>
         </is>
       </c>
-      <c r="E25" s="103" t="inlineStr">
+      <c r="B26" s="104" t="n"/>
+      <c r="C26" s="105" t="n"/>
+      <c r="D26" s="103" t="inlineStr">
         <is>
           <t>داشبورد  08_Dash</t>
         </is>
       </c>
+      <c r="E26" s="104" t="n"/>
+      <c r="F26" s="105" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="29">
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="B11:J11"/>
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="B13:J13"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="B10:D10"/>
+    <mergeCell ref="G24:I24"/>
     <mergeCell ref="B9:J9"/>
+    <mergeCell ref="D25:F25"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G25:I25"/>
     <mergeCell ref="G16:I16"/>
     <mergeCell ref="B5:J5"/>
+    <mergeCell ref="D26:F26"/>
     <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:J3"/>
@@ -1784,13 +1865,13 @@
     <hyperlink ref="D15" location="Sum!A8" display="خلاصه"/>
     <hyperlink ref="G15" location="Help!A8" display="راهنما"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId8"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.28" right="0.28" top="0.45" bottom="0.5" header="0.3" footer="0.3"/>
